--- a/Data/CERP_PBC_Summary_Data.xlsx
+++ b/Data/CERP_PBC_Summary_Data.xlsx
@@ -39494,6 +39494,286 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>45890</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>45890</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>100</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>45874</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>100</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>45874</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>45874</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>45874</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3" t="n">
+        <v>45875</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>85.71</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>45875</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.43</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AP30" s="3" t="n">
+        <v>45875</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>45916</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>100</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>45916</v>
+      </c>
+      <c r="H31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>90</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>45902</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>100</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>45902</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>45903</v>
+      </c>
+      <c r="W31" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>85.71</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>45904</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="AK31" s="3" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AP31" s="3" t="n">
+        <v>45903</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Data/CERP_PBC_Summary_Data.xlsx
+++ b/Data/CERP_PBC_Summary_Data.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t>CR-E1_LiveMean</t>
   </si>
@@ -1520,6 +1520,9 @@
   <si>
     <t xml:space="preserve">Winter 2025</t>
   </si>
+  <si>
+    <t xml:space="preserve">Spring 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -10661,6 +10664,777 @@
         <v>20</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>60</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L35" t="n">
+        <v>60</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O35" t="n">
+        <v>40</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>80</v>
+      </c>
+      <c r="CB35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CC35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E36" t="n">
+        <v>40</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H36" t="n">
+        <v>80</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L36" t="n">
+        <v>40</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O36" t="n">
+        <v>40</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>40</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V36" t="n">
+        <v>80</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>40</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H37" t="n">
+        <v>60</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S37" t="n">
+        <v>40</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V37" t="n">
+        <v>80</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BN37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>80</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -13084,6 +13858,314 @@
       <c r="CW12"/>
       <c r="CX12"/>
     </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>784</v>
+      </c>
+      <c r="H13" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1309.87</v>
+      </c>
+      <c r="L13" t="n">
+        <v>745.89</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O13" t="n">
+        <v>312</v>
+      </c>
+      <c r="P13" t="n">
+        <v>238.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>130.65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>277.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>199.23</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>119.73</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>152.53</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>448.27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>397.08</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>740.27</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>819.41</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>180.53</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>133.74</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>464.27</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>436.53</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>171.93</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>425.86</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>48</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>707.73</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>180.71</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -14085,6 +15167,122 @@
       <c r="AJ12"/>
       <c r="AK12"/>
       <c r="AL12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>398.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>441.76</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G13" t="n">
+        <v>810.93</v>
+      </c>
+      <c r="H13" t="n">
+        <v>744.07</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>117.42</v>
+      </c>
+      <c r="L13" t="n">
+        <v>168.04</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O13" t="n">
+        <v>183.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>151.21</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>405.69</v>
+      </c>
+      <c r="T13" t="n">
+        <v>593.39</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>69.87</v>
+      </c>
+      <c r="X13" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>484.53</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>283.14</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>257.24</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.09</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15300,6 +16498,164 @@
       <c r="AY12"/>
       <c r="AZ12"/>
     </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M13" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="O13" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="P13" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="U13" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="V13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -15855,6 +17211,68 @@
       <c r="R12"/>
       <c r="S12"/>
       <c r="T12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="I13" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="K13" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>19.96</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19739,6 +21157,345 @@
       </c>
       <c r="AK34" t="n">
         <v>73.33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="E35" t="n">
+        <v>40</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I35" t="n">
+        <v>50</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M35" t="n">
+        <v>60</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="U35" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E36" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I36" t="n">
+        <v>40</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M36" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>60</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U36" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AD36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M37" t="n">
+        <v>60</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U37" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AD37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AH37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -26337,6 +28094,597 @@
         <v>16.67</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="E35" t="n">
+        <v>76.35</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="H35" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="I35" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="J35" t="n">
+        <v>76.43</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="N35" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="O35" t="n">
+        <v>80.21</v>
+      </c>
+      <c r="P35" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="S35" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="T35" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="U35" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="V35" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="W35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="X35" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>8.53</v>
+      </c>
+      <c r="AM35" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AX35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>73.21</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>9.71</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H36" t="n">
+        <v>67.07</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J36" t="n">
+        <v>76.68</v>
+      </c>
+      <c r="K36" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="M36" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8.72</v>
+      </c>
+      <c r="O36" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>50</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="S36" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="T36" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="W36" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="X36" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AB36" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>46.96</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AG36" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AH36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="AX36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>73.1</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>75.34</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>69.1</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>68.57</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>68.57</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>68.57</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="I37" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="J37" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>69.17</v>
+      </c>
+      <c r="N37" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>69.17</v>
+      </c>
+      <c r="P37" t="n">
+        <v>9.13</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="S37" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="U37" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="W37" t="n">
+        <v>10</v>
+      </c>
+      <c r="X37" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AH37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>65.9</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>71.93</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -28983,6 +31331,235 @@
       </c>
       <c r="Y34" t="n">
         <v>8.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75.29</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="D35" t="n">
+        <v>77.56</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H35" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="J35" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.89</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N35" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="P35" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="R35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>65.03</v>
+      </c>
+      <c r="U35" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="W35" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="C36" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="D36" t="n">
+        <v>73.76</v>
+      </c>
+      <c r="E36" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="F36" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="J36" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="L36" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="M36"/>
+      <c r="N36" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="O36" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="P36" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>9.03</v>
+      </c>
+      <c r="R36" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="T36" t="n">
+        <v>70.26</v>
+      </c>
+      <c r="U36" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="V36" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="W36" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="C37" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="D37" t="n">
+        <v>69.54</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="H37" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="J37" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="N37" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="O37" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="P37" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>8.62</v>
+      </c>
+      <c r="R37" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="S37" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="T37" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="U37" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="V37" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -35237,6 +37814,548 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AG35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AN35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AU35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AL36"/>
+      <c r="AM36"/>
+      <c r="AN36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AU36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BB36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AG37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -38288,6 +41407,264 @@
       </c>
       <c r="AB35" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -46246,6 +49623,357 @@
         <v>1.23</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C28" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="K28" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V28" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>9.71</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C29" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V29" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X29" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I30" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K30" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="P30"/>
+      <c r="Q30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="R30"/>
+      <c r="S30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="T30"/>
+      <c r="U30" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="V30" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.71</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>9.53</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -47421,6 +51149,138 @@
         <v>4.29</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C28" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C29" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="E30" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I30" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="K30" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Data/CERP_PBC_Summary_Data.xlsx
+++ b/Data/CERP_PBC_Summary_Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr defaultThemeVersion="202300"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="8"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Dermo Station" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t>CR-E1_LiveMean</t>
   </si>
@@ -1518,7 +1518,10 @@
     <t>Fall 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Winter 2025</t>
+    <t>Winter 2025</t>
+  </si>
+  <si>
+    <t>Spring 2026</t>
   </si>
 </sst>
 </file>
@@ -9940,7 +9943,7 @@
         <v>45937</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="R32" t="n">
         <v>1.56</v>
@@ -9979,7 +9982,7 @@
         <v>80</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AE32" t="n">
         <v>0.42</v>
@@ -10021,7 +10024,7 @@
         <v>0.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AS32" t="n">
         <v>40</v>
@@ -10033,7 +10036,7 @@
         <v>0.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AW32" t="n">
         <v>60</v>
@@ -10093,7 +10096,7 @@
         <v>0.15</v>
       </c>
       <c r="BP32" t="n">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="BQ32" t="n">
         <v>60</v>
@@ -10132,7 +10135,7 @@
         <v>0.1</v>
       </c>
       <c r="CC32" t="n">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="CD32" t="n">
         <v>40</v>
@@ -10164,7 +10167,7 @@
         <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>1.75</v>
@@ -10308,7 +10311,7 @@
         <v>0.35</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="BC33" t="n">
         <v>80</v>
@@ -10350,7 +10353,7 @@
         <v>0.15</v>
       </c>
       <c r="BP33" t="n">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="BQ33" t="n">
         <v>60</v>
@@ -10487,7 +10490,7 @@
         <v>1.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AC34" t="n">
         <v>100</v>
@@ -10517,7 +10520,7 @@
         <v>0.9</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AM34" t="n">
         <v>100</v>
@@ -10553,7 +10556,7 @@
         <v>80</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AY34" t="n">
         <v>1.02</v>
@@ -10586,7 +10589,7 @@
         <v>0.1</v>
       </c>
       <c r="BI34" t="n">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="BJ34" t="n">
         <v>40</v>
@@ -10616,7 +10619,7 @@
         <v>0.15</v>
       </c>
       <c r="BS34" t="n">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="BT34" t="n">
         <v>60</v>
@@ -10637,7 +10640,7 @@
         <v>0.5</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="CA34" t="n">
         <v>100</v>
@@ -10658,6 +10661,777 @@
         <v>0.11</v>
       </c>
       <c r="CG34" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>60</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L35" t="n">
+        <v>60</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O35" t="n">
+        <v>40</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V35" t="n">
+        <v>100</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>80</v>
+      </c>
+      <c r="CB35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CC35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E36" t="n">
+        <v>40</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H36" t="n">
+        <v>80</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L36" t="n">
+        <v>40</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O36" t="n">
+        <v>40</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S36" t="n">
+        <v>40</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V36" t="n">
+        <v>80</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>40</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H37" t="n">
+        <v>60</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S37" t="n">
+        <v>40</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="V37" t="n">
+        <v>80</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>80</v>
+      </c>
+      <c r="BD37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BN37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>80</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>20</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CG37" t="n">
         <v>20</v>
       </c>
     </row>
@@ -10672,108 +11446,108 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="21.5703125" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="19.42578125" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="18.7109375" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="21.42578125" hidden="0" customWidth="1"/>
-    <col min="26" max="26" width="18.7109375" hidden="0" customWidth="1"/>
-    <col min="27" max="27" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="29" max="29" width="21.42578125" hidden="0" customWidth="1"/>
-    <col min="30" max="30" width="18.7109375" hidden="0" customWidth="1"/>
-    <col min="31" max="31" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="32" max="32" width="12.85546875" hidden="0" customWidth="1"/>
-    <col min="33" max="33" width="21.7109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="19.44140625" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="15.88671875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="21.5546875" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="19.44140625" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="13.33203125" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="21.44140625" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="21.44140625" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="15.5546875" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="12.88671875" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="21.6640625" hidden="0" customWidth="1"/>
     <col min="34" max="34" width="19" hidden="0" customWidth="1"/>
-    <col min="35" max="35" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="36" max="36" width="12.85546875" hidden="0" customWidth="1"/>
-    <col min="37" max="37" width="21.7109375" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="15.5546875" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="12.88671875" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="21.6640625" hidden="0" customWidth="1"/>
     <col min="38" max="38" width="19" hidden="0" customWidth="1"/>
-    <col min="39" max="39" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="40" max="40" width="12.85546875" hidden="0" customWidth="1"/>
-    <col min="41" max="41" width="21.7109375" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="15.5546875" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="12.88671875" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="21.6640625" hidden="0" customWidth="1"/>
     <col min="42" max="42" width="19" hidden="0" customWidth="1"/>
-    <col min="43" max="43" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="44" max="44" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="45" max="45" width="21.42578125" hidden="0" customWidth="1"/>
-    <col min="46" max="46" width="18.7109375" hidden="0" customWidth="1"/>
-    <col min="47" max="47" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="48" max="48" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="49" max="49" width="21.42578125" hidden="0" customWidth="1"/>
-    <col min="50" max="50" width="18.7109375" hidden="0" customWidth="1"/>
-    <col min="51" max="51" width="15.28515625" hidden="0" customWidth="1"/>
-    <col min="52" max="52" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="53" max="53" width="21.42578125" hidden="0" customWidth="1"/>
-    <col min="54" max="54" width="18.7109375" hidden="0" customWidth="1"/>
-    <col min="55" max="55" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="56" max="56" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="57" max="57" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="58" max="58" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="59" max="59" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="60" max="60" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="61" max="61" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="62" max="62" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="63" max="63" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="64" max="64" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="65" max="65" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="66" max="66" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="67" max="67" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="68" max="68" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="69" max="69" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="70" max="70" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="71" max="71" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="72" max="72" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="73" max="73" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="74" max="74" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="75" max="75" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="76" max="76" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="77" max="77" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="78" max="78" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="79" max="79" width="15.140625" hidden="0" customWidth="1"/>
-    <col min="80" max="80" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="81" max="81" width="21.140625" hidden="0" customWidth="1"/>
-    <col min="82" max="82" width="18.5703125" hidden="0" customWidth="1"/>
-    <col min="83" max="83" width="15.140625" hidden="0" customWidth="1"/>
-    <col min="84" max="84" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="85" max="85" width="21.140625" hidden="0" customWidth="1"/>
-    <col min="86" max="86" width="18.5703125" hidden="0" customWidth="1"/>
-    <col min="87" max="87" width="15.140625" hidden="0" customWidth="1"/>
-    <col min="88" max="88" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="89" max="89" width="21.140625" hidden="0" customWidth="1"/>
-    <col min="90" max="90" width="18.5703125" hidden="0" customWidth="1"/>
-    <col min="91" max="91" width="14.7109375" hidden="0" customWidth="1"/>
+    <col min="43" max="43" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="44" max="44" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="45" max="45" width="21.44140625" hidden="0" customWidth="1"/>
+    <col min="46" max="46" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="47" max="47" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="48" max="48" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="49" max="49" width="21.44140625" hidden="0" customWidth="1"/>
+    <col min="50" max="50" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="51" max="51" width="15.33203125" hidden="0" customWidth="1"/>
+    <col min="52" max="52" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="53" max="53" width="21.44140625" hidden="0" customWidth="1"/>
+    <col min="54" max="54" width="18.6640625" hidden="0" customWidth="1"/>
+    <col min="55" max="55" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="56" max="56" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="57" max="57" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="58" max="58" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="59" max="59" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="60" max="60" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="61" max="61" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="62" max="62" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="63" max="63" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="64" max="64" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="65" max="65" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="66" max="66" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="67" max="67" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="68" max="68" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="69" max="69" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="70" max="70" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="71" max="71" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="72" max="72" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="73" max="73" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="74" max="74" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="75" max="75" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="76" max="76" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="77" max="77" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="78" max="78" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="79" max="79" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="80" max="80" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="81" max="81" width="21.109375" hidden="0" customWidth="1"/>
+    <col min="82" max="82" width="18.5546875" hidden="0" customWidth="1"/>
+    <col min="83" max="83" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="84" max="84" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="85" max="85" width="21.109375" hidden="0" customWidth="1"/>
+    <col min="86" max="86" width="18.5546875" hidden="0" customWidth="1"/>
+    <col min="87" max="87" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="88" max="88" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="89" max="89" width="21.109375" hidden="0" customWidth="1"/>
+    <col min="90" max="90" width="18.5546875" hidden="0" customWidth="1"/>
+    <col min="91" max="91" width="14.6640625" hidden="0" customWidth="1"/>
     <col min="92" max="92" width="12" hidden="0" customWidth="1"/>
-    <col min="93" max="93" width="20.7109375" hidden="0" customWidth="1"/>
-    <col min="94" max="94" width="18.140625" hidden="0" customWidth="1"/>
-    <col min="95" max="95" width="14.7109375" hidden="0" customWidth="1"/>
+    <col min="93" max="93" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="94" max="94" width="18.109375" hidden="0" customWidth="1"/>
+    <col min="95" max="95" width="14.6640625" hidden="0" customWidth="1"/>
     <col min="96" max="96" width="12" hidden="0" customWidth="1"/>
-    <col min="97" max="97" width="20.7109375" hidden="0" customWidth="1"/>
-    <col min="98" max="98" width="18.140625" hidden="0" customWidth="1"/>
-    <col min="99" max="99" width="14.7109375" hidden="0" customWidth="1"/>
+    <col min="97" max="97" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="98" max="98" width="18.109375" hidden="0" customWidth="1"/>
+    <col min="99" max="99" width="14.6640625" hidden="0" customWidth="1"/>
     <col min="100" max="100" width="12" hidden="0" customWidth="1"/>
-    <col min="101" max="101" width="20.7109375" hidden="0" customWidth="1"/>
-    <col min="102" max="102" width="18.140625" hidden="0" customWidth="1"/>
+    <col min="101" max="101" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="102" max="102" width="18.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12959,10 +13733,6 @@
       <c r="B12" s="3" t="n">
         <v>45992</v>
       </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
       <c r="G12" t="n">
         <v>827.2</v>
       </c>
@@ -12970,7 +13740,7 @@
         <v>262.75</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J12" t="n">
         <v>0.03</v>
@@ -12979,7 +13749,7 @@
         <v>1392.27</v>
       </c>
       <c r="L12" t="n">
-        <v>553.8</v>
+        <v>553.79999999999995</v>
       </c>
       <c r="M12" t="n">
         <v>0.08</v>
@@ -12987,60 +13757,8 @@
       <c r="N12" t="n">
         <v>0.02</v>
       </c>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="X12"/>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12"/>
-      <c r="AB12"/>
-      <c r="AC12"/>
-      <c r="AD12"/>
-      <c r="AE12"/>
-      <c r="AF12"/>
-      <c r="AG12"/>
-      <c r="AH12"/>
-      <c r="AI12"/>
-      <c r="AJ12"/>
-      <c r="AK12"/>
-      <c r="AL12"/>
-      <c r="AM12"/>
-      <c r="AN12"/>
-      <c r="AO12"/>
-      <c r="AP12"/>
-      <c r="AQ12"/>
-      <c r="AR12"/>
-      <c r="AS12"/>
-      <c r="AT12"/>
-      <c r="AU12"/>
-      <c r="AV12"/>
-      <c r="AW12"/>
-      <c r="AX12"/>
-      <c r="AY12"/>
-      <c r="AZ12"/>
-      <c r="BA12"/>
-      <c r="BB12"/>
-      <c r="BC12"/>
-      <c r="BD12"/>
-      <c r="BE12"/>
-      <c r="BF12"/>
-      <c r="BG12"/>
-      <c r="BH12"/>
-      <c r="BI12"/>
-      <c r="BJ12"/>
-      <c r="BK12"/>
-      <c r="BL12"/>
-      <c r="BM12"/>
-      <c r="BN12"/>
       <c r="BO12" t="n">
-        <v>562.67</v>
+        <v>562.66999999999996</v>
       </c>
       <c r="BP12" t="n">
         <v>344.19</v>
@@ -13049,40 +13767,316 @@
         <v>0.13</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="BS12"/>
-      <c r="BT12"/>
-      <c r="BU12"/>
-      <c r="BV12"/>
-      <c r="BW12"/>
-      <c r="BX12"/>
-      <c r="BY12"/>
-      <c r="BZ12"/>
-      <c r="CA12"/>
-      <c r="CB12"/>
-      <c r="CC12"/>
-      <c r="CD12"/>
-      <c r="CE12"/>
-      <c r="CF12"/>
-      <c r="CG12"/>
-      <c r="CH12"/>
-      <c r="CI12"/>
-      <c r="CJ12"/>
-      <c r="CK12"/>
-      <c r="CL12"/>
-      <c r="CM12"/>
-      <c r="CN12"/>
-      <c r="CO12"/>
-      <c r="CP12"/>
-      <c r="CQ12"/>
-      <c r="CR12"/>
-      <c r="CS12"/>
-      <c r="CT12"/>
-      <c r="CU12"/>
-      <c r="CV12"/>
-      <c r="CW12"/>
-      <c r="CX12"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>784</v>
+      </c>
+      <c r="H13" t="n">
+        <v>292.42</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1309.8699999999999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>745.89</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O13" t="n">
+        <v>312</v>
+      </c>
+      <c r="P13" t="n">
+        <v>238.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>325.60000000000002</v>
+      </c>
+      <c r="X13" t="n">
+        <v>130.65</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>277.60000000000002</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>199.23</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>119.73</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>152.53</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>448.27</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>397.08</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>740.27</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>819.41</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>180.53</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>133.74</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>464.27</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>436.53</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>171.93</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>552.79999999999995</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>425.86</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>48</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>18.670000000000002</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>707.73</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>180.71</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.02</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13095,11 +14089,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14032,7 +15026,7 @@
         <v>262.75</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F12" t="n">
         <v>0.03</v>
@@ -14041,7 +15035,7 @@
         <v>1392.27</v>
       </c>
       <c r="H12" t="n">
-        <v>553.8</v>
+        <v>553.79999999999995</v>
       </c>
       <c r="I12" t="n">
         <v>0.08</v>
@@ -14049,24 +15043,8 @@
       <c r="J12" t="n">
         <v>0.02</v>
       </c>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="X12"/>
-      <c r="Y12"/>
-      <c r="Z12"/>
       <c r="AA12" t="n">
-        <v>562.67</v>
+        <v>562.66999999999996</v>
       </c>
       <c r="AB12" t="n">
         <v>344.19</v>
@@ -14075,16 +15053,124 @@
         <v>0.13</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="AE12"/>
-      <c r="AF12"/>
-      <c r="AG12"/>
-      <c r="AH12"/>
-      <c r="AI12"/>
-      <c r="AJ12"/>
-      <c r="AK12"/>
-      <c r="AL12"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>398.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>441.76</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G13" t="n">
+        <v>810.93</v>
+      </c>
+      <c r="H13" t="n">
+        <v>744.07</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>117.42</v>
+      </c>
+      <c r="L13" t="n">
+        <v>168.04</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O13" t="n">
+        <v>183.29</v>
+      </c>
+      <c r="P13" t="n">
+        <v>151.21</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>405.69</v>
+      </c>
+      <c r="T13" t="n">
+        <v>593.39</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>69.87</v>
+      </c>
+      <c r="X13" t="n">
+        <v>110.41</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>484.53</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>283.14</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>257.24</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.09</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14097,8 +15183,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10" hidden="0" customWidth="1"/>
@@ -15237,8 +16323,6 @@
       <c r="B12" s="3" t="n">
         <v>45992</v>
       </c>
-      <c r="C12"/>
-      <c r="D12"/>
       <c r="E12" t="n">
         <v>39.81</v>
       </c>
@@ -15251,54 +16335,170 @@
       <c r="H12" t="n">
         <v>16.04</v>
       </c>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="X12"/>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12"/>
-      <c r="AB12"/>
-      <c r="AC12"/>
-      <c r="AD12"/>
-      <c r="AE12"/>
-      <c r="AF12"/>
-      <c r="AG12"/>
-      <c r="AH12"/>
       <c r="AI12" t="n">
         <v>49.98</v>
       </c>
       <c r="AJ12" t="n">
         <v>23.02</v>
       </c>
-      <c r="AK12"/>
-      <c r="AL12"/>
-      <c r="AM12"/>
-      <c r="AN12"/>
-      <c r="AO12"/>
-      <c r="AP12"/>
-      <c r="AQ12"/>
-      <c r="AR12"/>
-      <c r="AS12"/>
-      <c r="AT12"/>
-      <c r="AU12"/>
-      <c r="AV12"/>
-      <c r="AW12"/>
-      <c r="AX12"/>
-      <c r="AY12"/>
-      <c r="AZ12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M13" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="O13" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="P13" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="R13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="U13" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="V13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="X13" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>36.950000000000003</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>36.369999999999997</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>43.96</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>42.61</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>18.93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15311,8 +16511,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="9" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15837,24 +17037,74 @@
       <c r="F12" t="n">
         <v>16.04</v>
       </c>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
       <c r="O12" t="n">
         <v>49.98</v>
       </c>
       <c r="P12" t="n">
         <v>23.02</v>
       </c>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="I13" t="n">
+        <v>31.18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="K13" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="N13" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="O13" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="R13" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>19.96</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19437,7 +20687,7 @@
         <v>1.03</v>
       </c>
       <c r="L32" t="n">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>66.67</v>
@@ -19458,7 +20708,7 @@
         <v>45937</v>
       </c>
       <c r="S32" t="n">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="T32" t="n">
         <v>0.67</v>
@@ -19482,7 +20732,7 @@
         <v>45938</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="AB32" t="n">
         <v>0.68</v>
@@ -19562,7 +20812,7 @@
         <v>0.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="Q33" t="n">
         <v>53.33</v>
@@ -19583,7 +20833,7 @@
         <v>45965</v>
       </c>
       <c r="W33" t="n">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="X33" t="n">
         <v>0.63</v>
@@ -19648,7 +20898,7 @@
         <v>46000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H34" t="n">
         <v>0.76</v>
@@ -19708,10 +20958,10 @@
         <v>45994</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AC34" t="n">
         <v>40</v>
@@ -19739,6 +20989,345 @@
       </c>
       <c r="AK34" t="n">
         <v>73.33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="E35" t="n">
+        <v>40</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I35" t="n">
+        <v>50</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M35" t="n">
+        <v>60</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="U35" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E36" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I36" t="n">
+        <v>40</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M36" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>60</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="U36" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AD36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E37" t="n">
+        <v>50</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M37" t="n">
+        <v>60</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U37" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="AD37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AH37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -19752,71 +21341,71 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="20.140625" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="16.5703125" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.44140625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="20.109375" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="16.5546875" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="16.5546875" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="20" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="20.140625" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="20.85546875" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="20.140625" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="26" max="26" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="27" max="27" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="28" max="28" width="20.85546875" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="13.44140625" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="20.109375" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="19.44140625" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="20.88671875" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="20.109375" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="20.88671875" hidden="0" customWidth="1"/>
     <col min="29" max="29" width="20" hidden="0" customWidth="1"/>
-    <col min="30" max="30" width="17.42578125" hidden="0" customWidth="1"/>
-    <col min="31" max="31" width="17.42578125" hidden="0" customWidth="1"/>
-    <col min="32" max="32" width="17.42578125" hidden="0" customWidth="1"/>
-    <col min="33" max="33" width="20.7109375" hidden="0" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" hidden="0" customWidth="1"/>
-    <col min="35" max="35" width="19.5703125" hidden="0" customWidth="1"/>
-    <col min="36" max="36" width="16.85546875" hidden="0" customWidth="1"/>
-    <col min="37" max="37" width="18.85546875" hidden="0" customWidth="1"/>
-    <col min="38" max="38" width="16.140625" hidden="0" customWidth="1"/>
-    <col min="39" max="39" width="20.28515625" hidden="0" customWidth="1"/>
-    <col min="40" max="40" width="19.5703125" hidden="0" customWidth="1"/>
-    <col min="41" max="41" width="16.85546875" hidden="0" customWidth="1"/>
-    <col min="42" max="42" width="16.85546875" hidden="0" customWidth="1"/>
-    <col min="43" max="43" width="16.85546875" hidden="0" customWidth="1"/>
-    <col min="44" max="44" width="20.28515625" hidden="0" customWidth="1"/>
-    <col min="45" max="45" width="19.42578125" hidden="0" customWidth="1"/>
-    <col min="46" max="46" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="47" max="47" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="48" max="48" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="49" max="49" width="20.140625" hidden="0" customWidth="1"/>
-    <col min="50" max="50" width="12.28515625" hidden="0" customWidth="1"/>
-    <col min="51" max="51" width="19.140625" hidden="0" customWidth="1"/>
-    <col min="52" max="52" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="53" max="53" width="18.42578125" hidden="0" customWidth="1"/>
-    <col min="54" max="54" width="15.7109375" hidden="0" customWidth="1"/>
-    <col min="55" max="55" width="19.85546875" hidden="0" customWidth="1"/>
-    <col min="56" max="56" width="19.140625" hidden="0" customWidth="1"/>
-    <col min="57" max="57" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="58" max="58" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="59" max="59" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="60" max="60" width="19.85546875" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="17.44140625" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="20.6640625" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="19.5546875" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="16.88671875" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="18.88671875" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="16.109375" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="19.5546875" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="16.88671875" hidden="0" customWidth="1"/>
+    <col min="42" max="42" width="16.88671875" hidden="0" customWidth="1"/>
+    <col min="43" max="43" width="16.88671875" hidden="0" customWidth="1"/>
+    <col min="44" max="44" width="20.33203125" hidden="0" customWidth="1"/>
+    <col min="45" max="45" width="19.44140625" hidden="0" customWidth="1"/>
+    <col min="46" max="46" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="47" max="47" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="48" max="48" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="49" max="49" width="20.109375" hidden="0" customWidth="1"/>
+    <col min="50" max="50" width="12.33203125" hidden="0" customWidth="1"/>
+    <col min="51" max="51" width="19.109375" hidden="0" customWidth="1"/>
+    <col min="52" max="52" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="53" max="53" width="18.44140625" hidden="0" customWidth="1"/>
+    <col min="54" max="54" width="15.6640625" hidden="0" customWidth="1"/>
+    <col min="55" max="55" width="19.88671875" hidden="0" customWidth="1"/>
+    <col min="56" max="56" width="19.109375" hidden="0" customWidth="1"/>
+    <col min="57" max="57" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="58" max="58" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="59" max="59" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="60" max="60" width="19.88671875" hidden="0" customWidth="1"/>
     <col min="61" max="61" width="19" hidden="0" customWidth="1"/>
-    <col min="62" max="62" width="16.28515625" hidden="0" customWidth="1"/>
-    <col min="63" max="63" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="64" max="64" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="65" max="65" width="19.7109375" hidden="0" customWidth="1"/>
+    <col min="62" max="62" width="16.33203125" hidden="0" customWidth="1"/>
+    <col min="63" max="63" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="64" max="64" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="65" max="65" width="19.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22852,10 +24441,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="10" t="n">
         <v>45474</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="10" t="n">
         <v>45489</v>
       </c>
       <c r="C17" t="n">
@@ -23049,10 +24638,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="10" t="n">
         <v>45505</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="10" t="n">
         <v>45517</v>
       </c>
       <c r="C18" t="n">
@@ -23240,10 +24829,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="10" t="n">
         <v>45536</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="10" t="n">
         <v>45547</v>
       </c>
       <c r="C19" t="n">
@@ -23437,10 +25026,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="10" t="n">
         <v>45566</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="10" t="n">
         <v>45588</v>
       </c>
       <c r="C20" t="n">
@@ -23622,10 +25211,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="10" t="n">
         <v>45597</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="10" t="n">
         <v>45609</v>
       </c>
       <c r="C21" t="n">
@@ -23813,10 +25402,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="10" t="n">
         <v>45627</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="10" t="n">
         <v>45636</v>
       </c>
       <c r="C22" t="n">
@@ -24004,10 +25593,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="10" t="n">
         <v>45658</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="10" t="n">
         <v>45670</v>
       </c>
       <c r="C23" t="n">
@@ -24201,10 +25790,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="10" t="n">
         <v>45689</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="10" t="n">
         <v>45691</v>
       </c>
       <c r="C24" t="n">
@@ -24398,10 +25987,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="10" t="n">
         <v>45717</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="10" t="n">
         <v>45719</v>
       </c>
       <c r="C25" t="n">
@@ -24595,10 +26184,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="10" t="n">
         <v>45748</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="10" t="n">
         <v>45762</v>
       </c>
       <c r="C26" t="n">
@@ -24786,10 +26375,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="10" t="n">
         <v>45778</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="10" t="n">
         <v>45791</v>
       </c>
       <c r="C27" t="n">
@@ -24983,10 +26572,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="10" t="n">
         <v>45809</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="10" t="n">
         <v>45825</v>
       </c>
       <c r="C28" t="n">
@@ -25177,10 +26766,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="10" t="n">
         <v>45839</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="10" t="n">
         <v>45862</v>
       </c>
       <c r="C29" t="n">
@@ -25371,10 +26960,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="10" t="n">
         <v>45870</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="10" t="n">
         <v>45890</v>
       </c>
       <c r="C30" t="n">
@@ -25565,10 +27154,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="10" t="n">
         <v>45901</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="10" t="n">
         <v>45916</v>
       </c>
       <c r="C31" t="n">
@@ -25759,10 +27348,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="10" t="n">
         <v>45931</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="10" t="n">
         <v>45944</v>
       </c>
       <c r="C32" t="n">
@@ -25822,7 +27411,6 @@
       <c r="U32" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="V32"/>
       <c r="W32" t="n">
         <v>100</v>
       </c>
@@ -25850,7 +27438,6 @@
       <c r="AE32" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AF32"/>
       <c r="AG32" t="n">
         <v>100</v>
       </c>
@@ -25914,12 +27501,11 @@
       <c r="BA32" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="BB32"/>
       <c r="BC32" t="n">
         <v>100</v>
       </c>
       <c r="BD32" t="n">
-        <v>66.4</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="BE32" t="n">
         <v>11.77</v>
@@ -25950,17 +27536,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="10" t="n">
         <v>45962</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="10" t="n">
         <v>45973</v>
       </c>
       <c r="C33" t="n">
         <v>71.83</v>
       </c>
       <c r="D33" t="n">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="E33" t="n">
         <v>78.06</v>
@@ -25972,13 +27558,13 @@
         <v>46.67</v>
       </c>
       <c r="H33" t="n">
-        <v>79.6</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="I33" t="n">
-        <v>16.01</v>
+        <v>16.010000000000002</v>
       </c>
       <c r="J33" t="n">
-        <v>76.43</v>
+        <v>76.430000000000007</v>
       </c>
       <c r="K33" t="n">
         <v>7.92</v>
@@ -25990,13 +27576,13 @@
         <v>77.03</v>
       </c>
       <c r="N33" t="n">
-        <v>18.31</v>
+        <v>18.309999999999999</v>
       </c>
       <c r="O33" t="n">
         <v>78.53</v>
       </c>
       <c r="P33" t="n">
-        <v>18.15</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="Q33" t="n">
         <v>43.33</v>
@@ -26040,8 +27626,6 @@
       <c r="AD33" t="n">
         <v>10.3</v>
       </c>
-      <c r="AE33"/>
-      <c r="AF33"/>
       <c r="AG33" t="n">
         <v>100</v>
       </c>
@@ -26097,13 +27681,13 @@
         <v>45966</v>
       </c>
       <c r="AY33" t="n">
-        <v>67.57</v>
+        <v>67.569999999999993</v>
       </c>
       <c r="AZ33" t="n">
         <v>15.05</v>
       </c>
       <c r="BA33" t="n">
-        <v>71.82</v>
+        <v>71.819999999999993</v>
       </c>
       <c r="BB33" t="n">
         <v>14.08</v>
@@ -26143,20 +27727,20 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="10" t="n">
         <v>46000</v>
       </c>
       <c r="C34" t="n">
-        <v>69.6</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="D34" t="n">
         <v>15.86</v>
       </c>
       <c r="E34" t="n">
-        <v>80.57</v>
+        <v>80.569999999999993</v>
       </c>
       <c r="F34" t="n">
         <v>11.4</v>
@@ -26180,16 +27764,16 @@
         <v>26.67</v>
       </c>
       <c r="M34" t="n">
-        <v>71.4</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="N34" t="n">
-        <v>18.17</v>
+        <v>18.170000000000002</v>
       </c>
       <c r="O34" t="n">
         <v>76.33</v>
       </c>
       <c r="P34" t="n">
-        <v>16.19</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="Q34" t="n">
         <v>20</v>
@@ -26222,7 +27806,7 @@
         <v>56.67</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.03</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="AB34" t="n">
         <v>60</v>
@@ -26231,12 +27815,11 @@
         <v>46.33</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.38</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="AE34" t="n">
         <v>59</v>
       </c>
-      <c r="AF34"/>
       <c r="AG34" t="n">
         <v>96.67</v>
       </c>
@@ -26298,7 +27881,7 @@
         <v>14.71</v>
       </c>
       <c r="BA34" t="n">
-        <v>71.4</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="BB34" t="n">
         <v>13.82</v>
@@ -26334,7 +27917,598 @@
         <v>12.57</v>
       </c>
       <c r="BM34" t="n">
+        <v>16.670000000000002</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>74.97</v>
+      </c>
+      <c r="D35" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="E35" t="n">
+        <v>76.35</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="H35" t="n">
+        <v>78.63</v>
+      </c>
+      <c r="I35" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="J35" t="n">
+        <v>76.43</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="M35" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="N35" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="O35" t="n">
+        <v>80.21</v>
+      </c>
+      <c r="P35" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="S35" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="T35" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="U35" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="V35" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="W35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="X35" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>8.53</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>54.13</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AX35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>71.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>73.21</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>9.71</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>68.23</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="E36" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H36" t="n">
+        <v>67.07</v>
+      </c>
+      <c r="I36" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J36" t="n">
+        <v>76.68</v>
+      </c>
+      <c r="K36" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="L36" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="M36" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="N36" t="n">
+        <v>8.72</v>
+      </c>
+      <c r="O36" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>50</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="S36" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="T36" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>46.96</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AH36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="AX36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>73.1</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>75.34</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>69.1</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>68.57</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>67.86</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>68.57</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>68.57</v>
+      </c>
+      <c r="F37" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="I37" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="J37" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>69.17</v>
+      </c>
+      <c r="N37" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>69.17</v>
+      </c>
+      <c r="P37" t="n">
+        <v>9.13</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="S37" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="U37" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="W37" t="n">
+        <v>10</v>
+      </c>
+      <c r="X37" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="AG37" t="n">
         <v>16.67</v>
+      </c>
+      <c r="AH37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>59.46</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>66.47</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>65.9</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>71.93</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -26348,31 +28522,31 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="19" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" hidden="0" customWidth="1"/>
     <col min="15" max="15" width="15" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="16.85546875" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="18.42578125" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="17.28515625" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="16.88671875" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="14.33203125" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="18.44140625" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="15.6640625" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="17.33203125" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="14.5546875" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="16.44140625" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="13.88671875" hidden="0" customWidth="1"/>
     <col min="24" max="24" width="18" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="15.28515625" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="15.33203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28762,7 +30936,7 @@
         <v>68.63</v>
       </c>
       <c r="C32" t="n">
-        <v>18.1</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="D32" t="n">
         <v>85.72</v>
@@ -28839,10 +31013,10 @@
         <v>76.16</v>
       </c>
       <c r="C33" t="n">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="D33" t="n">
-        <v>77.54</v>
+        <v>77.540000000000006</v>
       </c>
       <c r="E33" t="n">
         <v>12.37</v>
@@ -28896,7 +31070,7 @@
         <v>15.28</v>
       </c>
       <c r="V33" t="n">
-        <v>64.57</v>
+        <v>64.569999999999993</v>
       </c>
       <c r="W33" t="n">
         <v>14.8</v>
@@ -28913,7 +31087,7 @@
         <v>45992</v>
       </c>
       <c r="B34" t="n">
-        <v>69.49</v>
+        <v>69.489999999999995</v>
       </c>
       <c r="C34" t="n">
         <v>17.25</v>
@@ -28983,6 +31157,237 @@
       </c>
       <c r="Y34" t="n">
         <v>8.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" t="n">
+        <v>75.29</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="D35" t="n">
+        <v>77.56</v>
+      </c>
+      <c r="E35" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H35" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="J35" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.89</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N35" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="P35" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="R35" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T35" t="n">
+        <v>65.03</v>
+      </c>
+      <c r="U35" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="W35" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="C36" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="D36" t="n">
+        <v>73.76</v>
+      </c>
+      <c r="E36" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="F36" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="J36" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N36" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="O36" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="P36" t="n">
+        <v>60.17</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>9.03</v>
+      </c>
+      <c r="R36" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="T36" t="n">
+        <v>70.26</v>
+      </c>
+      <c r="U36" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="V36" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="W36" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="C37" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="D37" t="n">
+        <v>69.54</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="H37" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="J37" t="n">
+        <v>51.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="N37" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="O37" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="P37" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>8.62</v>
+      </c>
+      <c r="R37" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="S37" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="T37" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="U37" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="V37" t="n">
+        <v>71.6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28996,61 +31401,61 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="9.28515625" hidden="0" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="9.28515625" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="9.5703125" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="9.5703125" hidden="0" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" hidden="0" customWidth="1"/>
-    <col min="27" max="27" width="11.85546875" hidden="0" customWidth="1"/>
-    <col min="28" max="28" width="9.28515625" hidden="0" customWidth="1"/>
-    <col min="29" max="29" width="11.85546875" hidden="0" customWidth="1"/>
-    <col min="30" max="30" width="9.28515625" hidden="0" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" hidden="0" customWidth="1"/>
-    <col min="32" max="32" width="9.28515625" hidden="0" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" hidden="0" customWidth="1"/>
-    <col min="34" max="34" width="11.42578125" hidden="0" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" hidden="0" customWidth="1"/>
-    <col min="36" max="36" width="11.42578125" hidden="0" customWidth="1"/>
-    <col min="37" max="37" width="8.85546875" hidden="0" customWidth="1"/>
-    <col min="38" max="38" width="11.42578125" hidden="0" customWidth="1"/>
-    <col min="39" max="39" width="8.85546875" hidden="0" customWidth="1"/>
-    <col min="40" max="40" width="12.28515625" hidden="0" customWidth="1"/>
-    <col min="41" max="41" width="11.42578125" hidden="0" customWidth="1"/>
-    <col min="42" max="42" width="8.85546875" hidden="0" customWidth="1"/>
-    <col min="43" max="43" width="11.42578125" hidden="0" customWidth="1"/>
-    <col min="44" max="44" width="8.85546875" hidden="0" customWidth="1"/>
-    <col min="45" max="45" width="11.42578125" hidden="0" customWidth="1"/>
-    <col min="46" max="46" width="8.85546875" hidden="0" customWidth="1"/>
-    <col min="47" max="47" width="12.5703125" hidden="0" customWidth="1"/>
-    <col min="48" max="48" width="11.7109375" hidden="0" customWidth="1"/>
-    <col min="50" max="50" width="11.7109375" hidden="0" customWidth="1"/>
-    <col min="52" max="52" width="11.7109375" hidden="0" customWidth="1"/>
-    <col min="54" max="54" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="55" max="55" width="11.28515625" hidden="0" customWidth="1"/>
-    <col min="56" max="56" width="8.7109375" hidden="0" customWidth="1"/>
-    <col min="57" max="57" width="11.28515625" hidden="0" customWidth="1"/>
-    <col min="58" max="58" width="8.7109375" hidden="0" customWidth="1"/>
-    <col min="59" max="59" width="11.28515625" hidden="0" customWidth="1"/>
-    <col min="60" max="60" width="8.7109375" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="11.88671875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="13.109375" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="9.5546875" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="9.5546875" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="9.5546875" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="11.88671875" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="9.33203125" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="11.88671875" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="9.33203125" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="11.88671875" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="9.33203125" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="12.33203125" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="11.44140625" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="11.44140625" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="8.88671875" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="11.44140625" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="8.88671875" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="12.33203125" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="11.44140625" hidden="0" customWidth="1"/>
+    <col min="42" max="42" width="8.88671875" hidden="0" customWidth="1"/>
+    <col min="43" max="43" width="11.44140625" hidden="0" customWidth="1"/>
+    <col min="44" max="44" width="8.88671875" hidden="0" customWidth="1"/>
+    <col min="45" max="45" width="11.44140625" hidden="0" customWidth="1"/>
+    <col min="46" max="46" width="8.88671875" hidden="0" customWidth="1"/>
+    <col min="47" max="47" width="12.5546875" hidden="0" customWidth="1"/>
+    <col min="48" max="48" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="50" max="50" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="52" max="52" width="11.6640625" hidden="0" customWidth="1"/>
+    <col min="54" max="54" width="12.109375" hidden="0" customWidth="1"/>
+    <col min="55" max="55" width="11.33203125" hidden="0" customWidth="1"/>
+    <col min="56" max="56" width="8.6640625" hidden="0" customWidth="1"/>
+    <col min="57" max="57" width="11.33203125" hidden="0" customWidth="1"/>
+    <col min="58" max="58" width="8.6640625" hidden="0" customWidth="1"/>
+    <col min="59" max="59" width="11.33203125" hidden="0" customWidth="1"/>
+    <col min="60" max="60" width="8.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34717,10 +37122,10 @@
         <v>30.1</v>
       </c>
       <c r="I32" t="n">
-        <v>17.49</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="J32" t="n">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="K32" t="n">
         <v>14.8</v>
@@ -34735,7 +37140,7 @@
         <v>3.08</v>
       </c>
       <c r="O32" t="n">
-        <v>9.2</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="P32" t="n">
         <v>4</v>
@@ -34804,7 +37209,7 @@
         <v>2.73</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AM32" t="n">
         <v>3.57</v>
@@ -34828,7 +37233,7 @@
         <v>0.8</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="AU32" s="3" t="n">
         <v>45938</v>
@@ -34974,16 +37379,16 @@
         <v>45965</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AI33" t="n">
         <v>0.46</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AL33" t="n">
         <v>0.04</v>
@@ -35099,7 +37504,7 @@
         <v>1.92</v>
       </c>
       <c r="O34" t="n">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P34" t="n">
         <v>1.42</v>
@@ -35144,10 +37549,10 @@
         <v>3.71</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AF34" t="n">
         <v>0.72</v>
@@ -35159,13 +37564,13 @@
         <v>2.42</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AJ34" t="n">
         <v>2.75</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AL34" t="n">
         <v>1.88</v>
@@ -35210,7 +37615,7 @@
         <v>0.71</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="BA34" t="n">
         <v>0.62</v>
@@ -35219,7 +37624,7 @@
         <v>45994</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="BD34" t="n">
         <v>0.46</v>
@@ -35235,6 +37640,546 @@
       </c>
       <c r="BH34" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AG35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AN35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AU35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AN36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AU36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BB36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AG37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -38040,7 +40985,7 @@
         <v>45944</v>
       </c>
       <c r="C33" t="n">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="D33" t="n">
         <v>3.14</v>
@@ -38061,7 +41006,7 @@
         <v>8.66</v>
       </c>
       <c r="J33" t="n">
-        <v>4.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>45937</v>
@@ -38097,13 +41042,13 @@
         <v>0.79</v>
       </c>
       <c r="V33" t="n">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>45938</v>
       </c>
       <c r="X33" t="n">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Y33" t="n">
         <v>0.51</v>
@@ -38162,7 +41107,7 @@
         <v>45965</v>
       </c>
       <c r="O34" t="n">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="P34" t="n">
         <v>0.26</v>
@@ -38242,7 +41187,7 @@
         <v>2.29</v>
       </c>
       <c r="M35" t="n">
-        <v>2.43</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>45993</v>
@@ -38266,7 +41211,7 @@
         <v>45994</v>
       </c>
       <c r="U35" t="n">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="V35" t="n">
         <v>0.8</v>
@@ -38288,6 +41233,264 @@
       </c>
       <c r="AB35" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -38301,7 +41504,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
@@ -43227,6 +46430,426 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C35" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="H35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="M35" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="O35" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="P35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="R35" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="T35" t="n">
+        <v>20</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="W35" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="X35" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AF35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AP35" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C36" t="n">
+        <v>90</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>46070</v>
+      </c>
+      <c r="H36" t="n">
+        <v>90</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="M36" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N36" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="O36" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="R36" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="U36" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="W36" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="X36" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AA36" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AF36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" s="3" t="n">
+        <v>46064</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="C37" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D37" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="H37" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="I37" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="M37" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="O37" t="n">
+        <v>20</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="R37" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="S37" t="n">
+        <v>40</v>
+      </c>
+      <c r="T37" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="W37" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="X37" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AA37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="3" t="n">
+        <v>46092</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -43238,45 +46861,45 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="19.33203125" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="15.88671875" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" hidden="0" customWidth="1"/>
     <col min="17" max="17" width="22" hidden="0" customWidth="1"/>
-    <col min="18" max="18" width="19.28515625" hidden="0" customWidth="1"/>
-    <col min="19" max="19" width="17.5703125" hidden="0" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" hidden="0" customWidth="1"/>
-    <col min="21" max="21" width="13.140625" hidden="0" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" hidden="0" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" hidden="0" customWidth="1"/>
-    <col min="24" max="24" width="22.28515625" hidden="0" customWidth="1"/>
-    <col min="25" max="25" width="19.5703125" hidden="0" customWidth="1"/>
-    <col min="26" max="26" width="17.85546875" hidden="0" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" hidden="0" customWidth="1"/>
-    <col min="28" max="28" width="16.140625" hidden="0" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" hidden="0" customWidth="1"/>
-    <col min="30" max="30" width="22.28515625" hidden="0" customWidth="1"/>
-    <col min="31" max="31" width="19.5703125" hidden="0" customWidth="1"/>
-    <col min="32" max="32" width="17.85546875" hidden="0" customWidth="1"/>
-    <col min="33" max="33" width="15.140625" hidden="0" customWidth="1"/>
-    <col min="34" max="34" width="16.140625" hidden="0" customWidth="1"/>
-    <col min="35" max="35" width="13.5703125" hidden="0" customWidth="1"/>
-    <col min="36" max="36" width="22.28515625" hidden="0" customWidth="1"/>
-    <col min="37" max="37" width="19.5703125" hidden="0" customWidth="1"/>
-    <col min="38" max="38" width="17.85546875" hidden="0" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="19.33203125" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="17.5546875" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="14.88671875" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="13.109375" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="16.109375" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="13.5546875" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="22.33203125" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="19.5546875" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="17.88671875" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="16.109375" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="13.5546875" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="22.33203125" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="19.5546875" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="17.88671875" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="15.109375" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="16.109375" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="13.5546875" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="22.33203125" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="19.5546875" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="17.88671875" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="15.109375" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45906,13 +49529,13 @@
         <v>12.22</v>
       </c>
       <c r="F25" t="n">
-        <v>9.21</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="G25" t="n">
         <v>3.07</v>
       </c>
       <c r="H25" t="n">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="I25" t="n">
         <v>10.11</v>
@@ -45936,7 +49559,7 @@
         <v>11.09</v>
       </c>
       <c r="P25" t="n">
-        <v>9.53</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="Q25" t="n">
         <v>19.21</v>
@@ -45960,7 +49583,7 @@
         <v>22.28</v>
       </c>
       <c r="X25" t="n">
-        <v>18.65</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="Y25" t="n">
         <v>6.04</v>
@@ -45999,7 +49622,7 @@
         <v>11.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="AL25" t="n">
         <v>1.76</v>
@@ -46016,7 +49639,7 @@
         <v>45965</v>
       </c>
       <c r="C26" t="n">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="D26" t="n">
         <v>6.91</v>
@@ -46049,7 +49672,7 @@
         <v>5.79</v>
       </c>
       <c r="N26" t="n">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="O26" t="n">
         <v>25.79</v>
@@ -46091,7 +49714,7 @@
         <v>2.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>38.48</v>
+        <v>38.479999999999997</v>
       </c>
       <c r="AC26" t="n">
         <v>22.67</v>
@@ -46156,10 +49779,10 @@
         <v>54.19</v>
       </c>
       <c r="J27" t="n">
-        <v>18.42</v>
+        <v>18.420000000000002</v>
       </c>
       <c r="K27" t="n">
-        <v>17.67</v>
+        <v>17.670000000000002</v>
       </c>
       <c r="L27" t="n">
         <v>9.52</v>
@@ -46177,7 +49800,7 @@
         <v>22.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>18.65</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="R27" t="n">
         <v>6.73</v>
@@ -46192,7 +49815,7 @@
         <v>45993</v>
       </c>
       <c r="V27" t="n">
-        <v>35.16</v>
+        <v>35.159999999999997</v>
       </c>
       <c r="W27" t="n">
         <v>23.37</v>
@@ -46207,7 +49830,7 @@
         <v>6.12</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AB27" t="n">
         <v>25.71</v>
@@ -46244,6 +49867,354 @@
       </c>
       <c r="AM27" t="n">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C28" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>18.79</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="K28" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V28" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C29" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="K29" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="V29" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="X29" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I30" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="K30" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Q30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="S30" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="V30" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -47297,7 +51268,7 @@
         <v>45937</v>
       </c>
       <c r="C25" t="n">
-        <v>16.83</v>
+        <v>16.829999999999998</v>
       </c>
       <c r="D25" t="n">
         <v>9.18</v>
@@ -47309,7 +51280,7 @@
         <v>7.08</v>
       </c>
       <c r="G25" t="n">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H25" t="n">
         <v>1.97</v>
@@ -47321,7 +51292,7 @@
         <v>21.93</v>
       </c>
       <c r="K25" t="n">
-        <v>19.17</v>
+        <v>19.170000000000002</v>
       </c>
       <c r="L25" t="n">
         <v>5.68</v>
@@ -47394,7 +51365,7 @@
         <v>11.82</v>
       </c>
       <c r="F27" t="n">
-        <v>8.46</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="G27" t="n">
         <v>3.25</v>
@@ -47419,6 +51390,138 @@
       </c>
       <c r="N27" t="n">
         <v>4.29</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="C28" t="n">
+        <v>36.119999999999997</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35.630000000000003</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>46063</v>
+      </c>
+      <c r="C29" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I29" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="E30" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I30" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="K30" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="L30" t="n">
+        <v>8.11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.15</v>
       </c>
     </row>
   </sheetData>
